--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/24 08:03:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>08/24 08:03:39</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>378000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>46380.37</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>378000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>756000</t>
+          <t>46380.37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>92760.74</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>92760.74</t>
+          <t>46380.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/24 09:45:46</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>378000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>378000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46380.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>46380.37</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/24 08:03:39</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/24 09:45:46</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>46380</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46380</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.37</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12269.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/25 12:50:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12269</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/02 11:07:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12195</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12195</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12195.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/02 11:07:38</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12195</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12195</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.12</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/03 18:23:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5952.38</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5564.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/03 19:40:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5564</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/03 18:23:33</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5564.38</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/03 19:40:03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5564</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.38</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/04 19:57:15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11760.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/04 20:59:45</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11760</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/04 19:57:15</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11760.19</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,240 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/04 19:57:09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12048.19</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11760</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/07 17:02:49</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11904.76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/07 19:03:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,213 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/07 17:02:49</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/08 13:38:20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18181.82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18181.82</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18181.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/08 15:27:46</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18181.82</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18181.82</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/08 15:27:46</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>18181</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>79800</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>9388.24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18181</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.82</t>
+          <t>9388.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/09 14:13:29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13095.24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/09 12:13:06</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>79800</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>9388.24</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>79800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>189800</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22483.47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>9388.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22483.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/09 15:29:43</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9388</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>189800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22483.47</t>
+          <t>189800</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22483.47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9388</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22483.47</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13095.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/09 12:13:06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>79800</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>9388.24</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>9388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8333.33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22483.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9388</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>13095.47</t>
+          <t>8333.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/11 12:03:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8333</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8333.33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8333</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8333.33</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.33</t>
         </is>
       </c>
     </row>
